--- a/plan/pubgen/samples/DUAL_LANG/BAB_01_2025_no_div.xlsx
+++ b/plan/pubgen/samples/DUAL_LANG/BAB_01_2025_no_div.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\designcraft\plan\pubgen\samples\DUAL_LANG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E648987-19D4-45BD-8726-05809D861A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650D57C5-92DA-4825-AD69-5647576A52FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="28800" windowHeight="9285" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="28800" windowHeight="9285" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COVER" sheetId="7" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="81">
   <si>
     <t>Warungbambu</t>
   </si>
@@ -287,9 +287,6 @@
   </si>
   <si>
     <t>F:\GitHub\designcraft\plan\pubgen\samples\DUAL_LANG\A02.rtf</t>
-  </si>
-  <si>
-    <t>F:\GitHub\designcraft\plan\pubgen\samples\DUAL_LANG\images\city_skyline.jpg</t>
   </si>
   <si>
     <t>EAST KARAWANG DISTRICT IN FIGURES</t>
@@ -823,7 +820,7 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -871,7 +868,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -879,7 +876,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -887,7 +884,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +941,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -978,7 +975,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -986,7 +983,7 @@
         <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -994,7 +991,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -1002,7 +999,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1020,7 +1017,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1038,7 +1035,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1077,7 +1074,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1085,7 +1082,7 @@
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1093,15 +1090,15 @@
         <v>38</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1201,8 +1198,8 @@
       <c r="A9" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>56</v>
+      <c r="B9" s="6">
+        <v>4.32</v>
       </c>
       <c r="C9" s="6">
         <v>17.27</v>
@@ -1254,13 +1251,13 @@
     </row>
     <row r="14" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="C14" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
@@ -1268,13 +1265,13 @@
     </row>
     <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>76</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>77</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
@@ -1282,25 +1279,25 @@
     </row>
     <row r="16" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>80</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>81</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>

--- a/plan/pubgen/samples/DUAL_LANG/BAB_01_2025_no_div.xlsx
+++ b/plan/pubgen/samples/DUAL_LANG/BAB_01_2025_no_div.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\designcraft\plan\pubgen\samples\DUAL_LANG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\designcraft\plan\pubgen\samples\DUAL_LANG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650D57C5-92DA-4825-AD69-5647576A52FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E39E22D-4137-41D6-AFD8-A656EDD6C7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="28800" windowHeight="9285" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COVER" sheetId="7" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="80">
   <si>
     <t>Warungbambu</t>
   </si>
@@ -308,9 +308,6 @@
   </si>
   <si>
     <t>R01.rtf</t>
-  </si>
-  <si>
-    <t>R01_en.rtf</t>
   </si>
   <si>
     <t>infografik_01.png</t>
@@ -941,7 +938,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -975,7 +972,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -983,7 +980,7 @@
         <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -991,7 +988,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -999,7 +996,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1017,7 +1014,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1035,7 +1032,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1082,7 +1079,7 @@
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1098,7 +1095,7 @@
         <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1251,13 +1248,13 @@
     </row>
     <row r="14" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="C14" s="12" t="s">
         <v>73</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>74</v>
       </c>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
@@ -1265,13 +1262,13 @@
     </row>
     <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>75</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>76</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
@@ -1279,25 +1276,25 @@
     </row>
     <row r="16" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>79</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>80</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
